--- a/examples/result/enzyme_fva_core_model.xlsx
+++ b/examples/result/enzyme_fva_core_model.xlsx
@@ -443,1260 +443,1254 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>EZ_ENO</t>
+          <t>EZ_ALCD2x_inferred_0</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.009074587043031846</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>0.009436814255197242</v>
+        <v>0.0001765136740084519</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>EZ_PPS_inferred_0</t>
+          <t>EZ_GLUDy</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0001123404021548793</v>
+        <v>0.0002114471628408706</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>EZ_GLUN_inferred_0</t>
+          <t>EZ_GLCpts_inferred_0</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>0.002641324197990427</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0001123385016816537</v>
+        <v>0.002857818497363543</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>EZ_ACKr_inferred_1</t>
+          <t>EZ_TKT1_inferred_0</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0001390928968318685</v>
+        <v>0.0002778847591317513</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>EZ_PIt2r_inferred_0</t>
+          <t>EZ_ALCD2x_inferred_1</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>0</v>
       </c>
-      <c r="C6" t="n">
-        <v>0.0002372564592596385</v>
-      </c>
+      <c r="C6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>EZ_ACONTb_inferred_1</t>
+          <t>EZ_FBP_inferred_0</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0007608353000286038</v>
+        <v>0.0001765148396866148</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>EZ_NADTRHD_inferred_0</t>
+          <t>EZ_NADH16_inferred_0</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>0.02036988002808496</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0001123370618267643</v>
+        <v>0.02071174355809061</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>EZ_D_LACt2_inferred_1</t>
+          <t>EZ_ATPS4r</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>0.008721475826108238</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0001123268942198501</v>
+        <v>0.01024670576770198</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>EZ_PIt2r_inferred_1</t>
+          <t>EZ_AKGDH_inferred_0</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>0.0004946201782020303</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0002372154131588618</v>
+        <v>0.00070792942569338</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>EZ_ACKr_inferred_2</t>
+          <t>EZ_ALCD2x_inferred_2</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>0.000139093434266052</v>
+        <v>0.0001764637882696563</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>EZ_FORt2_inferred_0</t>
+          <t>EZ_GLNabc_inferred_0</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0001123255502163132</v>
+        <v>0.0001790511199182946</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>EZ_GLUSy_inferred_0</t>
+          <t>EZ_MALS_inferred_0</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0001123368347779564</v>
+        <v>0.0006377154597216646</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>EZ_PGM_inferred_1</t>
+          <t>EZ_GLUN_inferred_1</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0001964708732238936</v>
+        <v>0.0001765908210763302</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>EZ_PPCK_inferred_0</t>
+          <t>EZ_SUCOAS_inferred_0</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>0.0001759323919178156</v>
       </c>
       <c r="C15" t="n">
-        <v>0.0001123335326416509</v>
+        <v>0.0003624616021829431</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>EZ_GLNS_inferred_1</t>
+          <t>EZ_PTAr_inferred_1</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0.0001123361679967918</v>
+        <v>0.0002228983913655961</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>EZ_LDH_D_inferred_0</t>
+          <t>EZ_G6PDH2r</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>2.434092133114579e-05</v>
       </c>
       <c r="C17" t="n">
-        <v>0.0001123381501432366</v>
+        <v>0.0004822564086601156</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>EZ_FUM_inferred_2</t>
+          <t>EZ_PDH_inferred_0</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>0.0006600498154822134</v>
       </c>
       <c r="C18" t="n">
-        <v>0.0001207417320080517</v>
+        <v>0.002416464071477902</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>EZ_TPI</t>
+          <t>EZ_ENO</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.0008933930703679422</v>
+        <v>0.009012174994371378</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0009633398847103021</v>
+        <v>0.009721588989135683</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>EZ_D_LACt2_inferred_0</t>
+          <t>EZ_TKT2_inferred_1</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>0.0001123272691714644</v>
+        <v>0.0002776863374945345</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>EZ_FUM_inferred_1</t>
+          <t>EZ_MALt2_2_inferred_0</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>6.487552021015916e-05</v>
+        <v>0.0001803015384996037</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>EZ_PPC</t>
+          <t>EZ_PGI</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.003046254010579529</v>
+        <v>0.001693755358049936</v>
       </c>
       <c r="C22" t="n">
-        <v>0.003188815504013228</v>
+        <v>0.002383842395705301</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>EZ_ME2_inferred_0</t>
+          <t>EZ_GLUN_inferred_2</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0001100164283729544</v>
+        <v>0.0001767198838512129</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>EZ_THD2_inferred_0</t>
+          <t>EZ_ACALD_inferred_0</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0001568788382732986</v>
+        <v>0.0001764878256790669</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>EZ_PFL_inferred_0</t>
+          <t>EZ_TKT2_inferred_0</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.0009579625090352983</v>
+        <v>0</v>
       </c>
       <c r="C25" t="n">
-        <v>0.00168437677196467</v>
+        <v>0.0002601960743328581</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>EZ_ALCD2x_inferred_0</t>
+          <t>EZ_AKGt2r_inferred_0</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>0</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0001123341953650342</v>
+        <v>0.0001891685714537939</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>EZ_rib</t>
+          <t>EZ_TALA_inferred_0</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.001595073198684441</v>
+        <v>0</v>
       </c>
       <c r="C27" t="n">
-        <v>0.001704495136304193</v>
+        <v>0.0002371626329169941</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>EZ_rnap</t>
+          <t>EZ_PYK_inferred_1</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>0</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0001022423286951424</v>
+        <v>0.0004092681519826805</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>EZ_ME1_inferred_0</t>
+          <t>EZ_FORti_inferred_1</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>0</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0001100856472025256</v>
+        <v>0.000598587879640273</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>EZ_FBA_inferred_0</t>
+          <t>EZ_TKT1_inferred_1</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.0002865753290817703</v>
+        <v>0</v>
       </c>
       <c r="C30" t="n">
-        <v>0.0005200216106895079</v>
+        <v>0.0002617111028092051</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>EZ_FRUpts2_inferred_0</t>
+          <t>EZ_RPE_inferred_1</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>0</v>
       </c>
       <c r="C31" t="n">
-        <v>0.0001123379271755834</v>
+        <v>0.0002387392437891882</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>EZ_ADK1</t>
+          <t>EZ_SUCCt2_2_inferred_0</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3.58660801659016e-08</v>
+        <v>0</v>
       </c>
       <c r="C32" t="n">
-        <v>2.350721152100466e-05</v>
+        <v>0.0001803015384996037</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>EZ_SUCDi_inferred_0</t>
+          <t>EZ_GLUt2r_inferred_0</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>0</v>
       </c>
       <c r="C33" t="n">
-        <v>0.0001123346648256988</v>
+        <v>0.000176548105957847</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>EZ_TALA_inferred_1</t>
+          <t>EZ_FUMt2_2_inferred_0</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>0</v>
       </c>
       <c r="C34" t="n">
-        <v>0.0001598441468494184</v>
+        <v>0.0001764886332938692</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>EZ_PGM_inferred_0</t>
+          <t>EZ_ME2_inferred_0</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>0</v>
       </c>
       <c r="C35" t="n">
-        <v>0.0006333892125777412</v>
+        <v>0.0001765844389844022</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>EZ_TKT1_inferred_0</t>
+          <t>EZ_ADK1</t>
         </is>
       </c>
       <c r="B36" t="n">
         <v>0</v>
       </c>
       <c r="C36" t="n">
-        <v>0.0002097302694443104</v>
+        <v>0.0002047999100380611</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>EZ_ALCD2x_inferred_1</t>
+          <t>EZ_GAPD</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0</v>
+        <v>0.006017247331639781</v>
       </c>
       <c r="C37" t="n">
-        <v>0.0001123346714148603</v>
+        <v>0.006520109073363985</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>EZ_FBP_inferred_0</t>
+          <t>EZ_FBA_inferred_2</t>
         </is>
       </c>
       <c r="B38" t="n">
         <v>0</v>
       </c>
       <c r="C38" t="n">
-        <v>0.0001123340625643822</v>
+        <v>0.0006108502691106787</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>EZ_NADH16_inferred_0</t>
+          <t>EZ_RPI_inferred_0</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.02043476216353104</v>
+        <v>0</v>
       </c>
       <c r="C39" t="n">
-        <v>0.02060896102175221</v>
+        <v>0.0002072635459473204</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>EZ_ATPS4r</t>
+          <t>EZ_ACKr_inferred_0</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.009263639093260756</v>
+        <v>0</v>
       </c>
       <c r="C40" t="n">
-        <v>0.01013353792508979</v>
+        <v>0.0002051559480952094</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>EZ_AKGDH_inferred_0</t>
+          <t>EZ_FBP_inferred_1</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.0005247890663943632</v>
+        <v>0</v>
       </c>
       <c r="C41" t="n">
-        <v>0.0006704966498336691</v>
+        <v>0.0001766639431940427</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>EZ_ALCD2x_inferred_2</t>
+          <t>EZ_PGM_inferred_2</t>
         </is>
       </c>
       <c r="B42" t="n">
         <v>0</v>
       </c>
       <c r="C42" t="n">
-        <v>0.0001123331407314036</v>
+        <v>0.0008320239648205813</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>EZ_GLNabc_inferred_0</t>
+          <t>EZ_PGL</t>
         </is>
       </c>
       <c r="B43" t="n">
         <v>0</v>
       </c>
       <c r="C43" t="n">
-        <v>0.0001123350556306848</v>
+        <v>0.0003289465838189324</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>EZ_MALS_inferred_0</t>
+          <t>EZ_ACONTa_inferred_1</t>
         </is>
       </c>
       <c r="B44" t="n">
         <v>0</v>
       </c>
       <c r="C44" t="n">
-        <v>0.0004040336951334164</v>
+        <v>0.0008450336958292907</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>EZ_ACONTa_inferred_0</t>
+          <t>EZ_CYTBD_inferred_0</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0</v>
+        <v>0.003062544495944967</v>
       </c>
       <c r="C45" t="n">
-        <v>0.0007339234427336939</v>
+        <v>0.003258283342525717</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>EZ_ICL_inferred_0</t>
+          <t>EZ_PTAr_inferred_0</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.000333727810787453</v>
+        <v>0</v>
       </c>
       <c r="C46" t="n">
-        <v>0.000440925763699131</v>
+        <v>0.0002224521484446213</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>EZ_MALS_inferred_1</t>
+          <t>EZ_ACONTb_inferred_0</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>9.349997705188263e-05</v>
+        <v>0</v>
       </c>
       <c r="C47" t="n">
-        <v>0.0005300570920058604</v>
+        <v>0.0008532881690278219</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>EZ_LDH_D_inferred_1</t>
+          <t>EZ_FUM_inferred_0</t>
         </is>
       </c>
       <c r="B48" t="n">
         <v>0</v>
       </c>
       <c r="C48" t="n">
-        <v>0.0001123357770508348</v>
+        <v>0.000569616248521577</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>EZ_GLNS_inferred_0</t>
+          <t>EZ_ACONTa_inferred_0</t>
         </is>
       </c>
       <c r="B49" t="n">
         <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>0.0001101044004660687</v>
+        <v>0.0008532382981343312</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>EZ_RPE_inferred_0</t>
+          <t>EZ_RPI_inferred_1</t>
         </is>
       </c>
       <c r="B50" t="n">
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>0.0001692714747675279</v>
+        <v>0.000206803111973809</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>EZ_GLUN_inferred_2</t>
+          <t>EZ_PPS_inferred_0</t>
         </is>
       </c>
       <c r="B51" t="n">
         <v>0</v>
       </c>
       <c r="C51" t="n">
-        <v>0.0001101006615766784</v>
+        <v>0.0002148922634039968</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>EZ_GND</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr"/>
-      <c r="C52" t="n">
-        <v>0.001884379139679209</v>
-      </c>
+          <t>EZ_ACKr_inferred_2</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>0</v>
+      </c>
+      <c r="C52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>EZ_PYK_inferred_0</t>
+          <t>EZ_MALS_inferred_1</t>
         </is>
       </c>
       <c r="B53" t="n">
         <v>0</v>
       </c>
       <c r="C53" t="n">
-        <v>0.0002140187717524229</v>
+        <v>0.0005852845453509132</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>EZ_ICDHyr</t>
+          <t>EZ_PFK</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0</v>
+        <v>0.0002956990795958247</v>
       </c>
       <c r="C54" t="n">
-        <v>0.0001167425279117525</v>
+        <v>0.0004867083102919926</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>EZ_dummy_enzyme</t>
+          <t>EZ_PIt2r_inferred_0</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.02562439421619997</v>
+        <v>0</v>
       </c>
       <c r="C55" t="n">
-        <v>0.02573473348164533</v>
+        <v>0.0003039088233860976</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>EZ_ACONTb_inferred_0</t>
+          <t>EZ_FUM_inferred_2</t>
         </is>
       </c>
       <c r="B56" t="n">
         <v>0</v>
       </c>
       <c r="C56" t="n">
-        <v>0.0007477207845307942</v>
+        <v>0.000539435763344088</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>EZ_FORti_inferred_0</t>
+          <t>EZ_GLUSy_inferred_0</t>
         </is>
       </c>
       <c r="B57" t="n">
         <v>0</v>
       </c>
       <c r="C57" t="n">
-        <v>0.0005373798878886692</v>
+        <v>0.0001770867148440545</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>EZ_ACALD_inferred_1</t>
+          <t>EZ_ME1_inferred_0</t>
         </is>
       </c>
       <c r="B58" t="n">
         <v>0</v>
       </c>
       <c r="C58" t="n">
-        <v>0.0001123346714147241</v>
+        <v>0.0001766957222905049</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>EZ_FORt2_inferred_1</t>
+          <t>EZ_FRUpts2_inferred_0</t>
         </is>
       </c>
       <c r="B59" t="n">
         <v>0</v>
       </c>
       <c r="C59" t="n">
-        <v>0.0001123249875912135</v>
+        <v>0.0002114419264989216</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>EZ_PFK</t>
+          <t>EZ_SUCDi_inferred_0</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.0002992476300586336</v>
+        <v>0</v>
       </c>
       <c r="C60" t="n">
-        <v>0.000414334534477138</v>
+        <v>0.000182183247605007</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>EZ_MDH</t>
+          <t>EZ_TALA_inferred_1</t>
         </is>
       </c>
       <c r="B61" t="n">
         <v>0</v>
       </c>
       <c r="C61" t="n">
-        <v>0.0001291037753169689</v>
+        <v>0.0002372438348740474</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>EZ_PGK</t>
+          <t>EZ_PYK_inferred_0</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.004840549984826776</v>
-      </c>
-      <c r="C62" t="n">
-        <v>0.004975368971901542</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>EZ_CS</t>
+          <t>EZ_FUM_inferred_1</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.001999364762313249</v>
+        <v>0</v>
       </c>
       <c r="C63" t="n">
-        <v>0.002123025809320361</v>
+        <v>0.0005400436871130426</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>EZ_FUM_inferred_0</t>
+          <t>EZ_PGM_inferred_0</t>
         </is>
       </c>
       <c r="B64" t="n">
         <v>0</v>
       </c>
       <c r="C64" t="n">
-        <v>0.0004614631657304935</v>
+        <v>0.0008474147367717612</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>EZ_FRD7_inferred_0</t>
+          <t>EZ_PFL_inferred_0</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.0008524439976490995</v>
+        <v>0.0008537779580942678</v>
       </c>
       <c r="C65" t="n">
-        <v>0.0009737803886335195</v>
+        <v>0.00174552595111034</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>EZ_GLUt2r_inferred_0</t>
-        </is>
-      </c>
-      <c r="B66" t="n">
-        <v>0</v>
-      </c>
+          <t>EZ_GLNS_inferred_0</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr"/>
       <c r="C66" t="n">
-        <v>0.0001099939044324747</v>
+        <v>0.0001905974528017583</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>EZ_TKT2_inferred_0</t>
+          <t>EZ_FBA_inferred_0</t>
         </is>
       </c>
       <c r="B67" t="n">
         <v>0</v>
       </c>
       <c r="C67" t="n">
-        <v>0.0001920736444146023</v>
+        <v>0.0006632342929190549</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>EZ_RPI_inferred_1</t>
+          <t>EZ_MDH</t>
         </is>
       </c>
       <c r="B68" t="n">
         <v>0</v>
       </c>
       <c r="C68" t="n">
-        <v>0.0001213408170414094</v>
+        <v>0.0002079698383510538</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>EZ_RPE_inferred_1</t>
+          <t>EZ_FORt2_inferred_0</t>
         </is>
       </c>
       <c r="B69" t="n">
         <v>0</v>
       </c>
       <c r="C69" t="n">
-        <v>0.0001658424180382161</v>
+        <v>0.0001504308434876954</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>EZ_FUMt2_2_inferred_0</t>
+          <t>EZ_ACALD_inferred_1</t>
         </is>
       </c>
       <c r="B70" t="n">
         <v>0</v>
       </c>
       <c r="C70" t="n">
-        <v>0.0001123294477677432</v>
+        <v>0.0001803100182642751</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>EZ_SUCCt2_2_inferred_0</t>
+          <t>EZ_CS</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0</v>
+        <v>0.001962468042907953</v>
       </c>
       <c r="C71" t="n">
-        <v>0.0001123294477678183</v>
+        <v>0.002158199583264976</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>EZ_GLUDy</t>
+          <t>EZ_PPCK_inferred_0</t>
         </is>
       </c>
       <c r="B72" t="n">
         <v>0</v>
       </c>
       <c r="C72" t="n">
-        <v>0.0001125566209146842</v>
+        <v>0.0001766401262328534</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>EZ_AKGt2r_inferred_0</t>
+          <t>EZ_PGK</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0</v>
+        <v>0.004807895227916674</v>
       </c>
       <c r="C73" t="n">
-        <v>5.603079022115359e-05</v>
+        <v>0.00523861358115308</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>EZ_ACALD_inferred_0</t>
+          <t>EZ_GLNS_inferred_1</t>
         </is>
       </c>
       <c r="B74" t="n">
         <v>0</v>
       </c>
       <c r="C74" t="n">
-        <v>0.0001099563193544131</v>
+        <v>0.0001766513174922719</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>EZ_TKT1_inferred_1</t>
+          <t>EZ_PIt2r_inferred_1</t>
         </is>
       </c>
       <c r="B75" t="n">
         <v>0</v>
       </c>
       <c r="C75" t="n">
-        <v>0.0001580561826530979</v>
+        <v>0.0003475868059902044</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>EZ_TALA_inferred_0</t>
+          <t>EZ_ICDHyr</t>
         </is>
       </c>
       <c r="B76" t="n">
         <v>0</v>
       </c>
       <c r="C76" t="n">
-        <v>0.0001311011006037677</v>
+        <v>0.0001625630786219404</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>EZ_PYK_inferred_1</t>
+          <t>EZ_NADTRHD_inferred_0</t>
         </is>
       </c>
       <c r="B77" t="n">
         <v>0</v>
       </c>
       <c r="C77" t="n">
-        <v>0.0002645991230216869</v>
+        <v>0.0001766519199189091</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>EZ_GLCpts_inferred_0</t>
+          <t>EZ_dummy_enzyme</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.002665752352989586</v>
+        <v>0.02562439421619999</v>
       </c>
       <c r="C78" t="n">
-        <v>0.002795552626751214</v>
+        <v>0.02580149749627954</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>EZ_GAPD</t>
+          <t>EZ_FORti_inferred_0</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.006058115890451423</v>
+        <v>0</v>
       </c>
       <c r="C79" t="n">
-        <v>0.006348599006559323</v>
+        <v>0.0006020481647456006</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>EZ_FORti_inferred_1</t>
+          <t>EZ_FBA_inferred_1</t>
         </is>
       </c>
       <c r="B80" t="n">
         <v>0</v>
       </c>
       <c r="C80" t="n">
-        <v>0.0004728264662502488</v>
+        <v>0.0006108018486365912</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>EZ_FBA_inferred_2</t>
+          <t>EZ_ACONTb_inferred_1</t>
         </is>
       </c>
       <c r="B81" t="n">
         <v>0</v>
       </c>
       <c r="C81" t="n">
-        <v>0.0005274308119738309</v>
+        <v>0.0008713795424858842</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>EZ_PGI</t>
+          <t>EZ_ACKr_inferred_1</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.001708865122266108</v>
+        <v>0</v>
       </c>
       <c r="C82" t="n">
-        <v>0.002243943602249731</v>
+        <v>0.0001981379028436779</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>EZ_RPI_inferred_0</t>
+          <t>EZ_GLUN_inferred_0</t>
         </is>
       </c>
       <c r="B83" t="n">
         <v>0</v>
       </c>
       <c r="C83" t="n">
-        <v>0.0001437849404950207</v>
+        <v>0.0001765020218431426</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>EZ_PTAr_inferred_1</t>
+          <t>EZ_GND</t>
         </is>
       </c>
       <c r="B84" t="n">
         <v>0</v>
       </c>
       <c r="C84" t="n">
-        <v>0.0001354720394868158</v>
+        <v>0.00195388099718088</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>EZ_ACKr_inferred_0</t>
+          <t>EZ_RPE_inferred_0</t>
         </is>
       </c>
       <c r="B85" t="n">
         <v>0</v>
       </c>
       <c r="C85" t="n">
-        <v>0.0001362188701077582</v>
+        <v>0.0002373482823698213</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>EZ_TKT2_inferred_1</t>
+          <t>EZ_FRD7_inferred_0</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0</v>
+        <v>0.0008420828868824221</v>
       </c>
       <c r="C86" t="n">
-        <v>0.0001881169764263643</v>
+        <v>0.001058009142143876</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>EZ_FBP_inferred_1</t>
+          <t>EZ_TPI</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0</v>
+        <v>0.0008873460291387468</v>
       </c>
       <c r="C87" t="n">
-        <v>0.0001123385330967263</v>
+        <v>0.001161362098073611</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>EZ_PDH_inferred_0</t>
+          <t>EZ_D_LACt2_inferred_1</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.0007330326245162346</v>
+        <v>0</v>
       </c>
       <c r="C88" t="n">
-        <v>0.001183674588393717</v>
+        <v>0.0001765272009377835</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>EZ_PGM_inferred_2</t>
+          <t>EZ_LDH_D_inferred_0</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.0001416527909956287</v>
+        <v>0</v>
       </c>
       <c r="C89" t="n">
-        <v>0.0007719706757255787</v>
+        <v>0.0001766666492027138</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>EZ_MALt2_2_inferred_0</t>
+          <t>EZ_FORt2_inferred_1</t>
         </is>
       </c>
       <c r="B90" t="n">
         <v>0</v>
       </c>
       <c r="C90" t="n">
-        <v>0.0001123294477678183</v>
+        <v>0.0001765547242981715</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>EZ_PGL</t>
+          <t>EZ_PGM_inferred_1</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.0001108446246419602</v>
+        <v>0</v>
       </c>
       <c r="C91" t="n">
-        <v>0.0002564096614958223</v>
+        <v>0.0003202777050309765</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>EZ_GLUN_inferred_1</t>
+          <t>EZ_D_LACt2_inferred_0</t>
         </is>
       </c>
       <c r="B92" t="n">
         <v>0</v>
       </c>
       <c r="C92" t="n">
-        <v>0.000112338751412328</v>
+        <v>0.0001764517297057175</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>EZ_ACONTa_inferred_1</t>
+          <t>EZ_PPC</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0</v>
+        <v>0.003002266358330725</v>
       </c>
       <c r="C93" t="n">
-        <v>0.0007767377775852638</v>
+        <v>0.003210787257974243</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>EZ_G6PDH2r</t>
+          <t>EZ_THD2_inferred_0</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.0002018796811733871</v>
+        <v>0</v>
       </c>
       <c r="C94" t="n">
-        <v>0.0003768765518262297</v>
+        <v>0.000977098597674101</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>EZ_CYTBD_inferred_0</t>
+          <t>EZ_rib</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.003078599573414365</v>
+        <v>0.001641307257509645</v>
       </c>
       <c r="C95" t="n">
-        <v>0.003194520571151647</v>
+        <v>0.001830491027377453</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>EZ_SUCOAS_inferred_0</t>
+          <t>EZ_LDH_D_inferred_1</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.0001869694027107898</v>
+        <v>0</v>
       </c>
       <c r="C96" t="n">
-        <v>0.0003073572595713507</v>
+        <v>0.0001767295873386131</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>EZ_PTAr_inferred_0</t>
+          <t>EZ_rnap</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0</v>
+        <v>3.694852278094727e-06</v>
       </c>
       <c r="C97" t="n">
-        <v>0.0001383773538077009</v>
+        <v>0.00016579113180086</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>EZ_FBA_inferred_1</t>
+          <t>EZ_ICL_inferred_0</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0</v>
+        <v>0.0003291669556685513</v>
       </c>
       <c r="C98" t="n">
-        <v>0.0005464889781728723</v>
+        <v>0.0005492377468310767</v>
       </c>
     </row>
   </sheetData>
